--- a/testdata/data.xlsx
+++ b/testdata/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10188"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
     <t>brojRacunaEUR</t>
   </si>
   <si>
-    <t>snezana.nikolic</t>
+    <t>jelenamedela</t>
   </si>
   <si>
     <t>https://uat.dbp.nlb.si/web-retail/login</t>
@@ -1239,7 +1239,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="3">
-        <v>9128</v>
+        <v>2804</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>22</v>
@@ -1304,7 +1304,7 @@
         <v>34</v>
       </c>
       <c r="B3" s="3">
-        <v>2804</v>
+        <v>9128</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>22</v>
